--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567915386</v>
+        <v>46157.93097353277</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097353277</v>
+        <v>46157.93172318049</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172318049</v>
+        <v>46157.93399701626</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399701626</v>
+        <v>46157.93717628974</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717628974</v>
+        <v>46158.28216039295</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216039295</v>
+        <v>46158.29680744329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29680744329</v>
+        <v>46158.29814345381</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814345381</v>
+        <v>46158.33387059053</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387059053</v>
+        <v>46158.36856791365</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36856791365</v>
+        <v>46158.3728755131</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
